--- a/output/Table_A_Consensus.xlsx
+++ b/output/Table_A_Consensus.xlsx
@@ -446,7 +446,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>GPB_Beta</t>
+          <t>GPGLMM_Beta</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.40925694337762</v>
+        <v>20.4092569433776</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4.861818947385448</v>
+        <v>4.86181894738545</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.908428553329575</v>
+        <v>2.90842855332957</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.902862326127196</v>
+        <v>2.9028623261272</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3.464220310330981</v>
+        <v>3.46422031033098</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.816953337227628</v>
+        <v>1.81695333722763</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3.880368726620222</v>
+        <v>3.88036872662022</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.442338273424356</v>
+        <v>2.44233827342436</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.162061803490259</v>
+        <v>4.16206180246143</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2.663346366342831</v>
+        <v>2.66334636634283</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.108369413661768</v>
+        <v>2.10836941366177</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.818928734529762</v>
+        <v>1.81892873452976</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2.115635115655348</v>
+        <v>2.11563511565535</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.021066351469752</v>
+        <v>2.02106635146975</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1.776261051200127</v>
+        <v>1.77626105120013</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.448776468344013</v>
+        <v>2.44877646834401</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1.602196794647775</v>
+        <v>1.60219679464778</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1.606920379264805</v>
+        <v>1.60692037926481</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2.331609268077099</v>
+        <v>2.3316092680771</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2.369109973919756</v>
+        <v>2.36910997391976</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3.518544445713903</v>
+        <v>3.5185444457139</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-2.229403798158371</v>
+        <v>-2.22940379815837</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2.040065065873477</v>
+        <v>2.04006506587348</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1.798388998877293</v>
+        <v>1.79838899887729</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1.349603101118037</v>
+        <v>1.34960310111804</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.892190576366973</v>
+        <v>1.89219057636697</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1.198550994819425</v>
+        <v>1.19855099481943</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.743205442024038</v>
+        <v>2.74320544202404</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1.390615069263627</v>
+        <v>1.39061506926363</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1.816240308160169</v>
+        <v>1.81624030816017</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1.238689119210946</v>
+        <v>1.23868911921095</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1.192908936949605</v>
+        <v>1.19290893694961</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1420,7 +1420,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1.148568786857889</v>
+        <v>1.14856878685789</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1.424112527226896</v>
+        <v>1.4241125272269</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1.995843926473189</v>
+        <v>1.99584392647319</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1.612176023831581</v>
+        <v>1.61217602383158</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1.102396175506141</v>
+        <v>1.10239617550614</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1.516643720352822</v>
+        <v>1.51664372035282</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.9684344163561422</v>
+        <v>0.968434416356142</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1.293687793429769</v>
+        <v>1.29368779342977</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0.8534655049500293</v>
+        <v>0.853465504950029</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.586782381026024</v>
+        <v>1.58678238102602</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1.392738501417402</v>
+        <v>1.3927385014174</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1.152111692508914</v>
+        <v>1.15211169250891</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1.570037306493733</v>
+        <v>1.57003730649373</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1.509562356559962</v>
+        <v>1.50956235655996</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>-0.5883773127593658</v>
+        <v>-0.588377312759366</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1.437883942174412</v>
+        <v>1.43788394217441</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1.588862137212719</v>
+        <v>1.58886213721272</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1.171874868528516</v>
+        <v>1.17187486852852</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.713847634455382</v>
+        <v>1.71384763445538</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
